--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-related-person.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T13:57:06+00:00</t>
+    <t>2026-10-19T15:00:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-related-person.xlsx
+++ b/r4-core-154-polish-use-of-abbreviations-and-technical-terms-in-profiles/StructureDefinition-at-core-related-person.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T15:00:46+00:00</t>
+    <t>2026-10-20T05:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
